--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555903312</v>
+        <v>46157.93114241411</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114241411</v>
+        <v>46157.93137375887</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93137375887</v>
+        <v>46157.93384918063</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384918063</v>
+        <v>46157.93696519337</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696519337</v>
+        <v>46158.28205391228</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205391228</v>
+        <v>46158.29653365507</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653365507</v>
+        <v>46158.2980857302</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980857302</v>
+        <v>46158.33371215055</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371215055</v>
+        <v>46158.37222620055</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Январь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222620055</v>
+        <v>46158.37276074154</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
